--- a/doctors.xlsx
+++ b/doctors.xlsx
@@ -436,7 +436,7 @@
         <v>mon 09:00-17:00, tue 09:00-17:00, wed 09:00-17:00, thu 09:00-17:00, fri 09:00-16:00</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-05-14 16:00</v>
+        <v>2026-06-09 14:30</v>
       </c>
     </row>
     <row r="3">
@@ -456,7 +456,7 @@
         <v>mon 08:00-16:00, tue 08:00-16:00, wed 08:00-16:00, thu 08:00-16:00, fri 08:00-15:00</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-05-15 08:00</v>
+        <v>2026-06-10 12:30</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         <v>mon 10:00-18:00, tue 10:00-18:00, wed 10:00-18:00, thu 10:00-18:00, fri 10:00-17:00</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-05-14 18:30</v>
+        <v>2026-05-17 14:45</v>
       </c>
     </row>
     <row r="5">
@@ -496,7 +496,7 @@
         <v>mon 09:00-17:00, wed 09:00-17:00, fri 09:00-17:00</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-04-04 09:00</v>
+        <v>2026-06-10 09:00</v>
       </c>
     </row>
     <row r="6">
@@ -736,7 +736,7 @@
         <v>mon 09:00-17:00, tue 09:00-17:00, wed 09:00-17:00, thu 09:00-17:00, fri 09:00-16:00</v>
       </c>
       <c r="F17" t="str">
-        <v>2026-04-12 09:00</v>
+        <v>2026-05-20 15:00</v>
       </c>
     </row>
     <row r="18">
@@ -756,7 +756,7 @@
         <v>mon 10:00-18:00, wed 10:00-18:00, fri 10:00-18:00</v>
       </c>
       <c r="F18" t="str">
-        <v>NIL</v>
+        <v>2026-06-09 13:30</v>
       </c>
     </row>
     <row r="19">

--- a/doctors.xlsx
+++ b/doctors.xlsx
@@ -436,7 +436,7 @@
         <v>mon 09:00-17:00, tue 09:00-17:00, wed 09:00-17:00, thu 09:00-17:00, fri 09:00-16:00</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-06-09 14:30</v>
+        <v>2026-07-06 14:30</v>
       </c>
     </row>
     <row r="3">
@@ -456,7 +456,7 @@
         <v>mon 08:00-16:00, tue 08:00-16:00, wed 08:00-16:00, thu 08:00-16:00, fri 08:00-15:00</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-06-10 12:30</v>
+        <v>2026-07-07 09:30</v>
       </c>
     </row>
     <row r="4">

--- a/doctors.xlsx
+++ b/doctors.xlsx
@@ -436,7 +436,7 @@
         <v>mon 09:00-17:00, tue 09:00-17:00, wed 09:00-17:00, thu 09:00-17:00, fri 09:00-16:00</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-07-06 14:30</v>
+        <v>2026-07-08 09:00</v>
       </c>
     </row>
     <row r="3">
@@ -456,7 +456,7 @@
         <v>mon 08:00-16:00, tue 08:00-16:00, wed 08:00-16:00, thu 08:00-16:00, fri 08:00-15:00</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-07-07 09:30</v>
+        <v>2026-07-07 09:45</v>
       </c>
     </row>
     <row r="4">
@@ -476,7 +476,7 @@
         <v>mon 10:00-18:00, tue 10:00-18:00, wed 10:00-18:00, thu 10:00-18:00, fri 10:00-17:00</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-05-17 14:45</v>
+        <v>2026-07-07 10:15</v>
       </c>
     </row>
     <row r="5">
@@ -556,7 +556,7 @@
         <v>mon 09:00-16:00, tue 09:00-16:00, thu 09:00-16:00</v>
       </c>
       <c r="F8" t="str">
-        <v>NIL</v>
+        <v>2026-07-07 09:00</v>
       </c>
     </row>
     <row r="9">

--- a/doctors.xlsx
+++ b/doctors.xlsx
@@ -436,7 +436,7 @@
         <v>mon 09:00-17:00, tue 09:00-17:00, wed 09:00-17:00, thu 09:00-17:00, fri 09:00-16:00</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-07-08 09:00</v>
+        <v>2026-07-09 09:30</v>
       </c>
     </row>
     <row r="3">
@@ -496,7 +496,7 @@
         <v>mon 09:00-17:00, wed 09:00-17:00, fri 09:00-17:00</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-06-10 09:00</v>
+        <v>2026-07-09 13:15</v>
       </c>
     </row>
     <row r="6">

--- a/doctors.xlsx
+++ b/doctors.xlsx
@@ -436,7 +436,7 @@
         <v>mon 09:00-17:00, tue 09:00-17:00, wed 09:00-17:00, thu 09:00-17:00, fri 09:00-16:00</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-07-09 09:30</v>
+        <v>2026-07-09 13:55</v>
       </c>
     </row>
     <row r="3">
